--- a/Speciallægeloft/speciallægeloft_data/Region_Sjælland.xlsx
+++ b/Speciallægeloft/speciallægeloft_data/Region_Sjælland.xlsx
@@ -82,7 +82,7 @@
     <t>Datasæt 12 2024</t>
   </si>
   <si>
-    <t>Kørsel 15.4.2026 13.45.54</t>
+    <t>Kørsel 15.4.2026 14.35.18</t>
   </si>
   <si>
     <t>Gruppe: Region Sjælland</t>
